--- a/llm_risk/分类模板.xlsx
+++ b/llm_risk/分类模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>1、配置问题</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>徐子扬</t>
+  </si>
+  <si>
+    <t>陈南</t>
   </si>
   <si>
     <t>issue类1.1</t>
@@ -242,10 +245,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -751,19 +754,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -1986,220 +1989,291 @@
       <c r="C58" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D58" s="9"/>
+      <c r="D58" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
     </row>
     <row r="59" spans="1:24">
       <c r="A59" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B59" s="9"/>
       <c r="C59">
         <v>10</v>
       </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:24">
       <c r="A60" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B60" s="9"/>
       <c r="C60">
         <v>0</v>
       </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:24">
       <c r="A61" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B61" s="9"/>
       <c r="C61">
         <v>13</v>
       </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
     </row>
     <row r="62" spans="1:24">
       <c r="A62" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B62" s="9"/>
       <c r="C62">
         <v>6</v>
       </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
     </row>
     <row r="63" spans="1:24">
       <c r="A63" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63">
         <v>10</v>
       </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
     </row>
     <row r="64" spans="1:24">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:4">
       <c r="A65" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B65" s="9"/>
       <c r="C65">
         <v>4</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66">
         <v>9</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B67" s="9"/>
       <c r="C67">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B68" s="9"/>
       <c r="C68">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B70" s="9"/>
       <c r="C70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B71" s="9"/>
       <c r="C71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B72" s="9"/>
       <c r="C72">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B73" s="9"/>
       <c r="C73">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="D73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B75" s="9"/>
       <c r="C75">
         <v>29</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="D75">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B76" s="9"/>
       <c r="C76">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B77" s="9"/>
       <c r="C77">
         <v>6</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="D77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B78" s="9"/>
       <c r="C78">
         <v>4</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="D78">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B79" s="9"/>
       <c r="C79">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="D79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B81" s="9"/>
       <c r="C81">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B82" s="9"/>
       <c r="C82">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B84" s="9"/>
       <c r="C84">
         <v>41</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="D84">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B85" s="9"/>
       <c r="C85">
         <v>24</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="D85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B86" s="9"/>
       <c r="C86">
         <v>4</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
